--- a/excel/read_lop.xlsx
+++ b/excel/read_lop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1474CA23-3EBA-42B4-A2A5-26A842230069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C986039-E0F2-46D9-992B-C18745B4B435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Tên lớp</t>
   </si>
@@ -51,26 +51,23 @@
     <t>DCT1235</t>
   </si>
   <si>
-    <t>DCT1236</t>
-  </si>
-  <si>
-    <t>DCT1237</t>
-  </si>
-  <si>
-    <t>DCT1238</t>
-  </si>
-  <si>
-    <t>DCT1239</t>
-  </si>
-  <si>
-    <t>DCT1240</t>
+    <t>Trương Minh Vũ</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Hưng</t>
+  </si>
+  <si>
+    <t>Hệ điều hành</t>
+  </si>
+  <si>
+    <t>Lập trình Java</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +77,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -105,9 +110,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,36 +403,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.8984375" customWidth="1"/>
     <col min="2" max="4" width="8.796875" style="1"/>
-    <col min="5" max="5" width="10.8984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.796875" style="1"/>
+    <col min="5" max="5" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -430,14 +445,14 @@
       <c r="D2" s="1">
         <v>2</v>
       </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -450,111 +465,11 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="1">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
